--- a/diseases/d223/2010-2014.xlsx
+++ b/diseases/d223/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35984,7 +35984,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48848,7 +48848,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">

--- a/diseases/d223/2010-2014.xlsx
+++ b/diseases/d223/2010-2014.xlsx
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3422,7 +3422,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5030,7 +5030,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8648,7 +8648,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9050,7 +9050,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11462,7 +11462,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12668,7 +12668,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK71" t="inlineStr">
@@ -15080,7 +15080,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -15482,7 +15482,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -15884,7 +15884,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -16286,7 +16286,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -16688,7 +16688,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -17492,7 +17492,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -17894,7 +17894,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -18698,7 +18698,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19100,7 +19100,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -19502,7 +19502,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -19904,7 +19904,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20708,7 +20708,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21512,7 +21512,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21914,7 +21914,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22718,7 +22718,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23120,7 +23120,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23522,7 +23522,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23924,7 +23924,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -24326,7 +24326,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -25130,7 +25130,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -25532,7 +25532,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -26336,7 +26336,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -26738,7 +26738,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -27140,7 +27140,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -27542,7 +27542,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -28346,7 +28346,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -28748,7 +28748,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -29552,7 +29552,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -30356,7 +30356,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
@@ -30758,7 +30758,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -31160,7 +31160,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -31562,7 +31562,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
@@ -31964,7 +31964,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -32366,7 +32366,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -32768,7 +32768,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -33170,7 +33170,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -33572,7 +33572,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33974,7 +33974,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -34376,7 +34376,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34778,7 +34778,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -35180,7 +35180,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -35582,7 +35582,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35984,7 +35984,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -36386,7 +36386,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -36788,7 +36788,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -37190,7 +37190,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -37592,7 +37592,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
@@ -37994,7 +37994,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -38396,7 +38396,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -38798,7 +38798,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
@@ -39200,7 +39200,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -39602,7 +39602,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -40004,7 +40004,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK197" t="inlineStr">
@@ -40406,7 +40406,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -40808,7 +40808,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -41210,7 +41210,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK203" t="inlineStr">
@@ -41612,7 +41612,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -42014,7 +42014,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -42416,7 +42416,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK209" t="inlineStr">
@@ -42818,7 +42818,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -43220,7 +43220,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -43622,7 +43622,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -44024,7 +44024,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -44426,7 +44426,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -44828,7 +44828,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
@@ -45230,7 +45230,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -46034,7 +46034,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
@@ -46436,7 +46436,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -46838,7 +46838,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -47240,7 +47240,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -47642,7 +47642,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -48044,7 +48044,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -48446,7 +48446,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -48848,7 +48848,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.09.26.1</t>
+          <t>globalid-disease-ontology:2026.10.16.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
